--- a/output2/【河洛話注音】金剛般若波羅蜜經004.xlsx
+++ b/output2/【河洛話注音】金剛般若波羅蜜經004.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3BA2D2E-D3BF-4F81-861A-65DBC6C96980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{599F3F32-5C6D-4550-A84E-3B39D58762CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="31875" windowHeight="11295" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="10" r:id="rId1"/>
@@ -2797,6 +2797,9 @@
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="62" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
@@ -2813,9 +2816,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3618,7 +3618,7 @@
       <c r="Q3" s="83"/>
       <c r="R3" s="83"/>
       <c r="T3" s="92"/>
-      <c r="V3" s="98" t="s">
+      <c r="V3" s="99" t="s">
         <v>233</v>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       <c r="Q4" s="84"/>
       <c r="R4" s="84"/>
       <c r="S4" s="93"/>
-      <c r="V4" s="99"/>
+      <c r="V4" s="100"/>
     </row>
     <row r="5" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B5" s="57">
@@ -3690,7 +3690,7 @@
       <c r="Q5" s="80"/>
       <c r="R5" s="80"/>
       <c r="S5" s="94"/>
-      <c r="V5" s="99"/>
+      <c r="V5" s="100"/>
     </row>
     <row r="6" spans="2:22" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="58"/>
@@ -3725,7 +3725,7 @@
       <c r="Q6" s="85"/>
       <c r="R6" s="85"/>
       <c r="S6" s="95"/>
-      <c r="V6" s="99"/>
+      <c r="V6" s="100"/>
     </row>
     <row r="7" spans="2:22" s="49" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="55"/>
@@ -3746,7 +3746,7 @@
       <c r="Q7" s="83"/>
       <c r="R7" s="83"/>
       <c r="S7" s="66"/>
-      <c r="V7" s="99"/>
+      <c r="V7" s="100"/>
     </row>
     <row r="8" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="56"/>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="R8" s="84"/>
       <c r="S8" s="93"/>
-      <c r="V8" s="99"/>
+      <c r="V8" s="100"/>
     </row>
     <row r="9" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B9" s="57">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="S9" s="94"/>
       <c r="T9" s="92"/>
-      <c r="V9" s="99"/>
+      <c r="V9" s="100"/>
     </row>
     <row r="10" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="58"/>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="R10" s="85"/>
       <c r="S10" s="96"/>
-      <c r="V10" s="99"/>
+      <c r="V10" s="100"/>
     </row>
     <row r="11" spans="2:22" s="66" customFormat="1" ht="60" customHeight="1">
       <c r="B11" s="65"/>
@@ -3896,7 +3896,7 @@
       <c r="P11" s="83"/>
       <c r="Q11" s="83"/>
       <c r="R11" s="83"/>
-      <c r="V11" s="99"/>
+      <c r="V11" s="100"/>
     </row>
     <row r="12" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="56"/>
@@ -3942,7 +3942,7 @@
         <v>284</v>
       </c>
       <c r="S12" s="93"/>
-      <c r="V12" s="99"/>
+      <c r="V12" s="100"/>
     </row>
     <row r="13" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B13" s="57">
@@ -3995,7 +3995,7 @@
         <v>227</v>
       </c>
       <c r="S13" s="94"/>
-      <c r="V13" s="99"/>
+      <c r="V13" s="100"/>
     </row>
     <row r="14" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="58"/>
@@ -4041,7 +4041,7 @@
         <v>285</v>
       </c>
       <c r="S14" s="96"/>
-      <c r="V14" s="99"/>
+      <c r="V14" s="100"/>
     </row>
     <row r="15" spans="2:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="63"/>
@@ -4061,7 +4061,7 @@
       <c r="P15" s="83"/>
       <c r="Q15" s="83"/>
       <c r="R15" s="83"/>
-      <c r="V15" s="99"/>
+      <c r="V15" s="100"/>
     </row>
     <row r="16" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="56"/>
@@ -4101,7 +4101,7 @@
         <v>276</v>
       </c>
       <c r="S16" s="93"/>
-      <c r="V16" s="99"/>
+      <c r="V16" s="100"/>
     </row>
     <row r="17" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B17" s="57">
@@ -4129,7 +4129,7 @@
       <c r="J17" s="80" t="s">
         <v>195</v>
       </c>
-      <c r="K17" s="104" t="s">
+      <c r="K17" s="98" t="s">
         <v>362</v>
       </c>
       <c r="L17" s="80" t="s">
@@ -4154,7 +4154,7 @@
         <v>223</v>
       </c>
       <c r="S17" s="94"/>
-      <c r="V17" s="99"/>
+      <c r="V17" s="100"/>
     </row>
     <row r="18" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="58"/>
@@ -4194,7 +4194,7 @@
         <v>277</v>
       </c>
       <c r="S18" s="96"/>
-      <c r="V18" s="99"/>
+      <c r="V18" s="100"/>
     </row>
     <row r="19" spans="2:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="63"/>
@@ -4214,7 +4214,7 @@
       <c r="P19" s="83"/>
       <c r="Q19" s="83"/>
       <c r="R19" s="83"/>
-      <c r="V19" s="99"/>
+      <c r="V19" s="100"/>
     </row>
     <row r="20" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="56"/>
@@ -4258,7 +4258,7 @@
         <v>282</v>
       </c>
       <c r="S20" s="93"/>
-      <c r="V20" s="99"/>
+      <c r="V20" s="100"/>
     </row>
     <row r="21" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B21" s="57">
@@ -4311,7 +4311,7 @@
         <v>200</v>
       </c>
       <c r="S21" s="94"/>
-      <c r="V21" s="99"/>
+      <c r="V21" s="100"/>
     </row>
     <row r="22" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="58"/>
@@ -4355,7 +4355,7 @@
         <v>283</v>
       </c>
       <c r="S22" s="96"/>
-      <c r="V22" s="100"/>
+      <c r="V22" s="101"/>
     </row>
     <row r="23" spans="2:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="63"/>
@@ -4434,7 +4434,7 @@
       <c r="E25" s="80" t="s">
         <v>199</v>
       </c>
-      <c r="F25" s="104" t="s">
+      <c r="F25" s="98" t="s">
         <v>215</v>
       </c>
       <c r="G25" s="80" t="s">
@@ -5099,7 +5099,7 @@
       <c r="H41" s="80" t="s">
         <v>230</v>
       </c>
-      <c r="I41" s="104" t="s">
+      <c r="I41" s="98" t="s">
         <v>369</v>
       </c>
       <c r="J41" s="80" t="s">
@@ -9598,7 +9598,7 @@
       </c>
     </row>
     <row r="5" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="102" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -9616,7 +9616,7 @@
       <c r="G5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="101" t="s">
+      <c r="I5" s="102" t="s">
         <v>6</v>
       </c>
       <c r="J5" s="6" t="s">
@@ -9641,7 +9641,7 @@
       <c r="R5" s="10"/>
     </row>
     <row r="6" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B6" s="102"/>
+      <c r="B6" s="103"/>
       <c r="C6" s="11" t="s">
         <v>16</v>
       </c>
@@ -9661,7 +9661,7 @@
         <f>$B5 &amp; G$4</f>
         <v>陰入</v>
       </c>
-      <c r="I6" s="102"/>
+      <c r="I6" s="103"/>
       <c r="J6" s="11" t="s">
         <v>17</v>
       </c>
@@ -9683,7 +9683,7 @@
       <c r="Q6" s="14"/>
     </row>
     <row r="7" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B7" s="102"/>
+      <c r="B7" s="103"/>
       <c r="C7" s="15" t="s">
         <v>22</v>
       </c>
@@ -9699,7 +9699,7 @@
       <c r="G7" s="16">
         <v>30</v>
       </c>
-      <c r="I7" s="102"/>
+      <c r="I7" s="103"/>
       <c r="J7" s="15" t="s">
         <v>22</v>
       </c>
@@ -9721,7 +9721,7 @@
       <c r="Q7" s="14"/>
     </row>
     <row r="8" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B8" s="102"/>
+      <c r="B8" s="103"/>
       <c r="C8" s="11" t="s">
         <v>24</v>
       </c>
@@ -9737,7 +9737,7 @@
       <c r="G8" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="102"/>
+      <c r="I8" s="103"/>
       <c r="J8" s="18" t="s">
         <v>24</v>
       </c>
@@ -9759,7 +9759,7 @@
       <c r="Q8" s="14"/>
     </row>
     <row r="9" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B9" s="102"/>
+      <c r="B9" s="103"/>
       <c r="C9" s="11" t="s">
         <v>33</v>
       </c>
@@ -9775,7 +9775,7 @@
       <c r="G9" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="102"/>
+      <c r="I9" s="103"/>
       <c r="J9" s="11" t="s">
         <v>33</v>
       </c>
@@ -9797,7 +9797,7 @@
       <c r="Q9" s="14"/>
     </row>
     <row r="10" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B10" s="103"/>
+      <c r="B10" s="104"/>
       <c r="C10" s="11" t="s">
         <v>38</v>
       </c>
@@ -9813,7 +9813,7 @@
       <c r="G10" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="103"/>
+      <c r="I10" s="104"/>
       <c r="J10" s="11" t="s">
         <v>43</v>
       </c>
@@ -9836,7 +9836,7 @@
       <c r="R10" s="28"/>
     </row>
     <row r="11" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B11" s="101" t="s">
+      <c r="B11" s="102" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -9854,7 +9854,7 @@
       <c r="G11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="101" t="s">
+      <c r="I11" s="102" t="s">
         <v>48</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -9878,7 +9878,7 @@
       <c r="Q11" s="14"/>
     </row>
     <row r="12" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B12" s="102"/>
+      <c r="B12" s="103"/>
       <c r="C12" s="11" t="s">
         <v>16</v>
       </c>
@@ -9898,7 +9898,7 @@
         <f>$B11 &amp; G$4</f>
         <v>陽入</v>
       </c>
-      <c r="I12" s="102"/>
+      <c r="I12" s="103"/>
       <c r="J12" s="11" t="s">
         <v>17</v>
       </c>
@@ -9918,7 +9918,7 @@
       <c r="Q12" s="14"/>
     </row>
     <row r="13" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B13" s="102"/>
+      <c r="B13" s="103"/>
       <c r="C13" s="15" t="s">
         <v>22</v>
       </c>
@@ -9932,7 +9932,7 @@
       <c r="G13" s="16">
         <v>50</v>
       </c>
-      <c r="I13" s="102"/>
+      <c r="I13" s="103"/>
       <c r="J13" s="15" t="s">
         <v>22</v>
       </c>
@@ -9952,7 +9952,7 @@
       <c r="Q13" s="14"/>
     </row>
     <row r="14" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B14" s="102"/>
+      <c r="B14" s="103"/>
       <c r="C14" s="11" t="s">
         <v>24</v>
       </c>
@@ -9966,7 +9966,7 @@
       <c r="G14" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="I14" s="102"/>
+      <c r="I14" s="103"/>
       <c r="J14" s="11" t="s">
         <v>24</v>
       </c>
@@ -9986,7 +9986,7 @@
       <c r="Q14" s="14"/>
     </row>
     <row r="15" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B15" s="102"/>
+      <c r="B15" s="103"/>
       <c r="C15" s="11" t="s">
         <v>33</v>
       </c>
@@ -10000,7 +10000,7 @@
       <c r="G15" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="I15" s="102"/>
+      <c r="I15" s="103"/>
       <c r="J15" s="11" t="s">
         <v>33</v>
       </c>
@@ -10020,7 +10020,7 @@
       <c r="Q15" s="14"/>
     </row>
     <row r="16" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B16" s="103"/>
+      <c r="B16" s="104"/>
       <c r="C16" s="11" t="s">
         <v>38</v>
       </c>
@@ -10034,7 +10034,7 @@
       <c r="G16" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="I16" s="103"/>
+      <c r="I16" s="104"/>
       <c r="J16" s="11" t="s">
         <v>43</v>
       </c>
